--- a/docs/examples/TabularData/probe_prediction_results.xlsx
+++ b/docs/examples/TabularData/probe_prediction_results.xlsx
@@ -585,17 +585,17 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Nepheline</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.9999988675117493</v>
+        <v>0.9965018630027771</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.05284502729773521</v>
       </c>
       <c r="T2" t="n">
-        <v>5.249468699730642e-07</v>
+        <v>0.003323873272165656</v>
       </c>
     </row>
     <row r="3">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.999977707862854</v>
+        <v>0.9991823434829712</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.007933631539344788</v>
       </c>
       <c r="T3" t="n">
-        <v>1.971811252587941e-05</v>
+        <v>0.0007650943007320166</v>
       </c>
     </row>
     <row r="4">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.9996451735496521</v>
+        <v>0.9992684721946716</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001859319629147649</v>
+        <v>0.007989779114723206</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002753582666628063</v>
+        <v>0.0004946748958900571</v>
       </c>
     </row>
     <row r="5">
@@ -777,17 +777,17 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Apatite</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.9993444085121155</v>
+        <v>0.9922365546226501</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003275490133091807</v>
+        <v>0.07257344573736191</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003961411130148917</v>
+        <v>0.004257562104612589</v>
       </c>
     </row>
     <row r="6">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.9989423155784607</v>
+        <v>0.9996606111526489</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007126230280846357</v>
+        <v>0.003710616147145629</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001020474825054407</v>
+        <v>0.0002107734908349812</v>
       </c>
     </row>
     <row r="7">
@@ -905,17 +905,17 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Pyroxene</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.9999696612358093</v>
+        <v>0.9994847774505615</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.005109484773129225</v>
       </c>
       <c r="T7" t="n">
-        <v>1.837652780523058e-05</v>
+        <v>0.0002328975679120049</v>
       </c>
     </row>
     <row r="8">
@@ -969,17 +969,17 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Apatite</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.99945068359375</v>
+        <v>0.9999303817749023</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003797936718910933</v>
+        <v>0.0004228639591019601</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0005083190626464784</v>
+        <v>4.754763722303323e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1033,17 +1033,17 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Spinel_Group</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.9983274340629578</v>
+        <v>0.9960872530937195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00883977860212326</v>
+        <v>0.02976113185286522</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001239542034454644</v>
+        <v>0.002201012801378965</v>
       </c>
     </row>
     <row r="10">
@@ -1097,17 +1097,17 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Spinel_Group</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.9883076548576355</v>
+        <v>0.9993535280227661</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07921864837408066</v>
+        <v>0.009315812960267067</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01140241604298353</v>
+        <v>0.0005853030597791076</v>
       </c>
     </row>
     <row r="11">
@@ -1161,17 +1161,17 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Kalsilite</t>
+          <t>Pyroxene</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.9986979961395264</v>
+        <v>0.994616687297821</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009069421328604221</v>
+        <v>0.06462674587965012</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001277090748772025</v>
+        <v>0.004128655418753624</v>
       </c>
     </row>
     <row r="12">
@@ -1229,17 +1229,17 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0.9966036081314087</v>
+        <v>0.9796119928359985</v>
       </c>
       <c r="S12" t="n">
-        <v>0.009713606908917427</v>
+        <v>0.1231262907385826</v>
       </c>
       <c r="T12" t="n">
-        <v>0.002778664929792285</v>
+        <v>0.01578642427921295</v>
       </c>
     </row>
     <row r="13">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Leucite</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0.9951438307762146</v>
+        <v>0.9822190999984741</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01676768064498901</v>
+        <v>0.1119849905371666</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002024916931986809</v>
+        <v>0.01035896502435207</v>
       </c>
     </row>
     <row r="14">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0.9798195362091064</v>
+        <v>0.9810236096382141</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1350377947092056</v>
+        <v>0.1144321784377098</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01945960521697998</v>
+        <v>0.01088796369731426</v>
       </c>
     </row>
     <row r="15">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Nepheline</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>0.994264543056488</v>
+        <v>0.9847466945648193</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02196587435901165</v>
+        <v>0.09102648496627808</v>
       </c>
       <c r="T15" t="n">
-        <v>0.00263807806186378</v>
+        <v>0.01329232100397348</v>
       </c>
     </row>
     <row r="16">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0.9873798489570618</v>
+        <v>0.9912225604057312</v>
       </c>
       <c r="S16" t="n">
-        <v>0.07769082486629486</v>
+        <v>0.04795359447598457</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01226158160716295</v>
+        <v>0.004293879959732294</v>
       </c>
     </row>
     <row r="17">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Amphibole</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>0.9958904385566711</v>
+        <v>0.9900177717208862</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0266627948731184</v>
+        <v>0.08762029558420181</v>
       </c>
       <c r="T17" t="n">
-        <v>0.003813273040577769</v>
+        <v>0.009753241203725338</v>
       </c>
     </row>
     <row r="18">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0.9989967942237854</v>
+        <v>0.9955244660377502</v>
       </c>
       <c r="S18" t="n">
-        <v>0.003726644907146692</v>
+        <v>0.0307733416557312</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0009537860169075429</v>
+        <v>0.004395700059831142</v>
       </c>
     </row>
     <row r="19">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0.9987256526947021</v>
+        <v>0.983611524105072</v>
       </c>
       <c r="S19" t="n">
-        <v>0.005689052864909172</v>
+        <v>0.1095182299613953</v>
       </c>
       <c r="T19" t="n">
-        <v>0.001185146160423756</v>
+        <v>0.01566766761243343</v>
       </c>
     </row>
     <row r="20">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0.9938669800758362</v>
+        <v>0.9971137642860413</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03177675604820251</v>
+        <v>0.02106836065649986</v>
       </c>
       <c r="T20" t="n">
-        <v>0.006088011898100376</v>
+        <v>0.002826116746291518</v>
       </c>
     </row>
     <row r="21">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0.9896082282066345</v>
+        <v>0.9953747391700745</v>
       </c>
       <c r="S21" t="n">
-        <v>0.07021240144968033</v>
+        <v>0.02547967433929443</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01038573402911425</v>
+        <v>0.003834587289020419</v>
       </c>
     </row>
     <row r="22">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>0.9996674060821533</v>
+        <v>0.9970842003822327</v>
       </c>
       <c r="S22" t="n">
-        <v>0.00126859184820205</v>
+        <v>0.01695854961872101</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0003100514295510948</v>
+        <v>0.002823152812197804</v>
       </c>
     </row>
     <row r="23">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0.9997379779815674</v>
+        <v>0.9964252710342407</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0008097228710539639</v>
+        <v>0.02923373691737652</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0002327171387150884</v>
+        <v>0.003441707696765661</v>
       </c>
     </row>
     <row r="24">
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0.981284499168396</v>
+        <v>0.9977558851242065</v>
       </c>
       <c r="S24" t="n">
-        <v>0.115364134311676</v>
+        <v>0.01025390625</v>
       </c>
       <c r="T24" t="n">
-        <v>0.01865028776228428</v>
+        <v>0.002174620050936937</v>
       </c>
     </row>
     <row r="25">
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>0.9798330068588257</v>
+        <v>0.9947446584701538</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1211296766996384</v>
+        <v>0.03486256301403046</v>
       </c>
       <c r="T25" t="n">
-        <v>0.02016276121139526</v>
+        <v>0.003266238374635577</v>
       </c>
     </row>
     <row r="26">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Amphibole</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>0.9995723962783813</v>
+        <v>0.991304874420166</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001777370576746762</v>
+        <v>0.06445451080799103</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0002672738919500262</v>
+        <v>0.008551507256925106</v>
       </c>
     </row>
     <row r="27">
@@ -2245,17 +2245,17 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Pyroxene</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>0.999992311000824</v>
+        <v>0.9962275624275208</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.04069319739937782</v>
       </c>
       <c r="T27" t="n">
-        <v>5.794264325231779e-06</v>
+        <v>0.002816388616338372</v>
       </c>
     </row>
     <row r="28">
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>0.9999915361404419</v>
+        <v>0.999897301197052</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.001145121059380472</v>
       </c>
       <c r="T28" t="n">
-        <v>7.523232852690853e-06</v>
+        <v>8.369483839487657e-05</v>
       </c>
     </row>
     <row r="29">
@@ -2373,17 +2373,17 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Pyroxene</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>0.9964977502822876</v>
+        <v>0.9989087581634521</v>
       </c>
       <c r="S29" t="n">
-        <v>0.02419210597872734</v>
+        <v>0.0143753020092845</v>
       </c>
       <c r="T29" t="n">
-        <v>0.003457305021584034</v>
+        <v>0.001002874691039324</v>
       </c>
     </row>
     <row r="30">
@@ -2437,17 +2437,17 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Pyroxene</t>
+          <t>Rhombohedral_Oxides</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>0.9994881153106689</v>
+        <v>0.9996756315231323</v>
       </c>
       <c r="S30" t="n">
-        <v>0.003356378758326173</v>
+        <v>0.002477756701409817</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0004698123084381223</v>
+        <v>0.0001219477053382434</v>
       </c>
     </row>
     <row r="31">
@@ -2501,17 +2501,17 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Rhombohedral_Oxides</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>0.9996950626373291</v>
+        <v>0.9990442991256714</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001859319629147649</v>
+        <v>0.01001571863889694</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0002955057425424457</v>
+        <v>0.0005891235778108239</v>
       </c>
     </row>
     <row r="32">
@@ -2565,17 +2565,17 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Feldspar</t>
+          <t>Amphibole</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>0.9958404302597046</v>
+        <v>0.9974963665008545</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01584282703697681</v>
+        <v>0.008400708436965942</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002306803362444043</v>
+        <v>0.001571694621816278</v>
       </c>
     </row>
     <row r="33">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>0.9991370439529419</v>
+        <v>0.9978086352348328</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001524657709524035</v>
+        <v>0.00682284589856863</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0006168530089780688</v>
+        <v>0.001512945280410349</v>
       </c>
     </row>
     <row r="34">
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>0.9947973489761353</v>
+        <v>0.9960677623748779</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01945633813738823</v>
+        <v>0.02689206413924694</v>
       </c>
       <c r="T34" t="n">
-        <v>0.005022941157221794</v>
+        <v>0.003199208294972777</v>
       </c>
     </row>
     <row r="35">
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>0.9989180564880371</v>
+        <v>0.9980217814445496</v>
       </c>
       <c r="S35" t="n">
-        <v>0.003588119754567742</v>
+        <v>0.006875062361359596</v>
       </c>
       <c r="T35" t="n">
-        <v>0.0006879738648422062</v>
+        <v>0.001234445488080382</v>
       </c>
     </row>
     <row r="36">
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>0.9962781667709351</v>
+        <v>0.9981886148452759</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01081132330000401</v>
+        <v>0.00503308791667223</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003154989797621965</v>
+        <v>0.001227503293193877</v>
       </c>
     </row>
     <row r="37">
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>0.9871963262557983</v>
+        <v>0.9994080662727356</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0890805572271347</v>
+        <v>0.008347325026988983</v>
       </c>
       <c r="T37" t="n">
-        <v>0.0127456858754158</v>
+        <v>0.0005847936263307929</v>
       </c>
     </row>
     <row r="38">
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>0.9720520973205566</v>
+        <v>0.9982761144638062</v>
       </c>
       <c r="S38" t="n">
-        <v>0.144215002655983</v>
+        <v>0.01710901595652103</v>
       </c>
       <c r="T38" t="n">
-        <v>0.02777916379272938</v>
+        <v>0.001217948971316218</v>
       </c>
     </row>
     <row r="39">
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>0.9974048137664795</v>
+        <v>0.9895976185798645</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01807300373911858</v>
+        <v>0.09096785634756088</v>
       </c>
       <c r="T39" t="n">
-        <v>0.002582918154075742</v>
+        <v>0.006191977299749851</v>
       </c>
     </row>
     <row r="40">
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>0.9936922192573547</v>
+        <v>0.992967963218689</v>
       </c>
       <c r="S40" t="n">
-        <v>0.03961778804659843</v>
+        <v>0.06339669972658157</v>
       </c>
       <c r="T40" t="n">
-        <v>0.00629688985645771</v>
+        <v>0.003223435720428824</v>
       </c>
     </row>
     <row r="41">
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>0.9841128587722778</v>
+        <v>0.999022901058197</v>
       </c>
       <c r="S41" t="n">
-        <v>0.07917612791061401</v>
+        <v>0.009322208352386951</v>
       </c>
       <c r="T41" t="n">
-        <v>0.01588609255850315</v>
+        <v>0.0009644082165323198</v>
       </c>
     </row>
   </sheetData>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Amphibole</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.9958904385566711</v>
+        <v>0.9900177717208862</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0266627948731184</v>
+        <v>0.08762029558420181</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003813273040577769</v>
+        <v>0.009753241203725338</v>
       </c>
     </row>
     <row r="3">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.9989967942237854</v>
+        <v>0.9955244660377502</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003726644907146692</v>
+        <v>0.0307733416557312</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009537860169075429</v>
+        <v>0.004395700059831142</v>
       </c>
     </row>
     <row r="4">
@@ -3465,13 +3465,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.9987256526947021</v>
+        <v>0.983611524105072</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005689052864909172</v>
+        <v>0.1095182299613953</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001185146160423756</v>
+        <v>0.01566766761243343</v>
       </c>
     </row>
     <row r="5">
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.9938669800758362</v>
+        <v>0.9971137642860413</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03177675604820251</v>
+        <v>0.02106836065649986</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006088011898100376</v>
+        <v>0.002826116746291518</v>
       </c>
     </row>
     <row r="6">
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.9896082282066345</v>
+        <v>0.9953747391700745</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07021240144968033</v>
+        <v>0.02547967433929443</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01038573402911425</v>
+        <v>0.003834587289020419</v>
       </c>
     </row>
     <row r="7">
@@ -3669,13 +3669,13 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.9996674060821533</v>
+        <v>0.9970842003822327</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00126859184820205</v>
+        <v>0.01695854961872101</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003100514295510948</v>
+        <v>0.002823152812197804</v>
       </c>
     </row>
     <row r="8">
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.9997379779815674</v>
+        <v>0.9964252710342407</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0008097228710539639</v>
+        <v>0.02923373691737652</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002327171387150884</v>
+        <v>0.003441707696765661</v>
       </c>
     </row>
     <row r="9">
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.981284499168396</v>
+        <v>0.9977558851242065</v>
       </c>
       <c r="S9" t="n">
-        <v>0.115364134311676</v>
+        <v>0.01025390625</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01865028776228428</v>
+        <v>0.002174620050936937</v>
       </c>
     </row>
     <row r="10">
@@ -3873,13 +3873,13 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.9798330068588257</v>
+        <v>0.9947446584701538</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1211296766996384</v>
+        <v>0.03486256301403046</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02016276121139526</v>
+        <v>0.003266238374635577</v>
       </c>
     </row>
     <row r="11">
@@ -3937,17 +3937,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Amphibole</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.9995723962783813</v>
+        <v>0.991304874420166</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001777370576746762</v>
+        <v>0.06445451080799103</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0002672738919500262</v>
+        <v>0.008551507256925106</v>
       </c>
     </row>
   </sheetData>
@@ -4117,17 +4117,17 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Feldspar</t>
+          <t>Amphibole</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.9958404302597046</v>
+        <v>0.9974963665008545</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01584282703697681</v>
+        <v>0.008400708436965942</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002306803362444043</v>
+        <v>0.001571694621816278</v>
       </c>
     </row>
     <row r="3">
@@ -4185,13 +4185,13 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.9991370439529419</v>
+        <v>0.9978086352348328</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001524657709524035</v>
+        <v>0.00682284589856863</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006168530089780688</v>
+        <v>0.001512945280410349</v>
       </c>
     </row>
     <row r="4">
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.9947973489761353</v>
+        <v>0.9960677623748779</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01945633813738823</v>
+        <v>0.02689206413924694</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005022941157221794</v>
+        <v>0.003199208294972777</v>
       </c>
     </row>
     <row r="5">
@@ -4313,13 +4313,13 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.9989180564880371</v>
+        <v>0.9980217814445496</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003588119754567742</v>
+        <v>0.006875062361359596</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0006879738648422062</v>
+        <v>0.001234445488080382</v>
       </c>
     </row>
     <row r="6">
@@ -4377,13 +4377,13 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.9962781667709351</v>
+        <v>0.9981886148452759</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01081132330000401</v>
+        <v>0.00503308791667223</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003154989797621965</v>
+        <v>0.001227503293193877</v>
       </c>
     </row>
   </sheetData>
@@ -4553,17 +4553,17 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Nepheline</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.9999988675117493</v>
+        <v>0.9965018630027771</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.05284502729773521</v>
       </c>
       <c r="T2" t="n">
-        <v>5.249468699730642e-07</v>
+        <v>0.003323873272165656</v>
       </c>
     </row>
     <row r="3">
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.999977707862854</v>
+        <v>0.9991823434829712</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.007933631539344788</v>
       </c>
       <c r="T3" t="n">
-        <v>1.971811252587941e-05</v>
+        <v>0.0007650943007320166</v>
       </c>
     </row>
     <row r="4">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.9996451735496521</v>
+        <v>0.9992684721946716</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001859319629147649</v>
+        <v>0.007989779114723206</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002753582666628063</v>
+        <v>0.0004946748958900571</v>
       </c>
     </row>
     <row r="5">
@@ -4745,17 +4745,17 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Apatite</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.9993444085121155</v>
+        <v>0.9922365546226501</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003275490133091807</v>
+        <v>0.07257344573736191</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003961411130148917</v>
+        <v>0.004257562104612589</v>
       </c>
     </row>
     <row r="6">
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.9989423155784607</v>
+        <v>0.9996606111526489</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007126230280846357</v>
+        <v>0.003710616147145629</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001020474825054407</v>
+        <v>0.0002107734908349812</v>
       </c>
     </row>
     <row r="7">
@@ -4873,17 +4873,17 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Pyroxene</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.9999696612358093</v>
+        <v>0.9994847774505615</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.005109484773129225</v>
       </c>
       <c r="T7" t="n">
-        <v>1.837652780523058e-05</v>
+        <v>0.0002328975679120049</v>
       </c>
     </row>
     <row r="8">
@@ -4937,17 +4937,17 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Apatite</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.99945068359375</v>
+        <v>0.9999303817749023</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003797936718910933</v>
+        <v>0.0004228639591019601</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0005083190626464784</v>
+        <v>4.754763722303323e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5001,17 +5001,17 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Spinel_Group</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.9983274340629578</v>
+        <v>0.9960872530937195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00883977860212326</v>
+        <v>0.02976113185286522</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001239542034454644</v>
+        <v>0.002201012801378965</v>
       </c>
     </row>
     <row r="10">
@@ -5065,17 +5065,17 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Spinel_Group</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.9883076548576355</v>
+        <v>0.9993535280227661</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07921864837408066</v>
+        <v>0.009315812960267067</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01140241604298353</v>
+        <v>0.0005853030597791076</v>
       </c>
     </row>
     <row r="11">
@@ -5129,17 +5129,17 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Kalsilite</t>
+          <t>Pyroxene</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.9986979961395264</v>
+        <v>0.994616687297821</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009069421328604221</v>
+        <v>0.06462674587965012</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001277090748772025</v>
+        <v>0.004128655418753624</v>
       </c>
     </row>
     <row r="12">
@@ -5193,17 +5193,17 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Pyroxene</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0.999992311000824</v>
+        <v>0.9962275624275208</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.04069319739937782</v>
       </c>
       <c r="T12" t="n">
-        <v>5.794264325231779e-06</v>
+        <v>0.002816388616338372</v>
       </c>
     </row>
     <row r="13">
@@ -5261,13 +5261,13 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0.9999915361404419</v>
+        <v>0.999897301197052</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.001145121059380472</v>
       </c>
       <c r="T13" t="n">
-        <v>7.523232852690853e-06</v>
+        <v>8.369483839487657e-05</v>
       </c>
     </row>
     <row r="14">
@@ -5321,17 +5321,17 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Pyroxene</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0.9964977502822876</v>
+        <v>0.9989087581634521</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02419210597872734</v>
+        <v>0.0143753020092845</v>
       </c>
       <c r="T14" t="n">
-        <v>0.003457305021584034</v>
+        <v>0.001002874691039324</v>
       </c>
     </row>
     <row r="15">
@@ -5385,17 +5385,17 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Pyroxene</t>
+          <t>Rhombohedral_Oxides</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>0.9994881153106689</v>
+        <v>0.9996756315231323</v>
       </c>
       <c r="S15" t="n">
-        <v>0.003356378758326173</v>
+        <v>0.002477756701409817</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0004698123084381223</v>
+        <v>0.0001219477053382434</v>
       </c>
     </row>
     <row r="16">
@@ -5449,17 +5449,17 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Rhombohedral_Oxides</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0.9996950626373291</v>
+        <v>0.9990442991256714</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001859319629147649</v>
+        <v>0.01001571863889694</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0002955057425424457</v>
+        <v>0.0005891235778108239</v>
       </c>
     </row>
     <row r="17">
@@ -5517,13 +5517,13 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>0.9871963262557983</v>
+        <v>0.9994080662727356</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0890805572271347</v>
+        <v>0.008347325026988983</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0127456858754158</v>
+        <v>0.0005847936263307929</v>
       </c>
     </row>
     <row r="18">
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0.9720520973205566</v>
+        <v>0.9982761144638062</v>
       </c>
       <c r="S18" t="n">
-        <v>0.144215002655983</v>
+        <v>0.01710901595652103</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02777916379272938</v>
+        <v>0.001217948971316218</v>
       </c>
     </row>
     <row r="19">
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>0.9974048137664795</v>
+        <v>0.9895976185798645</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01807300373911858</v>
+        <v>0.09096785634756088</v>
       </c>
       <c r="T19" t="n">
-        <v>0.002582918154075742</v>
+        <v>0.006191977299749851</v>
       </c>
     </row>
     <row r="20">
@@ -5709,13 +5709,13 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0.9936922192573547</v>
+        <v>0.992967963218689</v>
       </c>
       <c r="S20" t="n">
-        <v>0.03961778804659843</v>
+        <v>0.06339669972658157</v>
       </c>
       <c r="T20" t="n">
-        <v>0.00629688985645771</v>
+        <v>0.003223435720428824</v>
       </c>
     </row>
     <row r="21">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0.9841128587722778</v>
+        <v>0.999022901058197</v>
       </c>
       <c r="S21" t="n">
-        <v>0.07917612791061401</v>
+        <v>0.009322208352386951</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01588609255850315</v>
+        <v>0.0009644082165323198</v>
       </c>
     </row>
   </sheetData>
@@ -5953,17 +5953,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.9966036081314087</v>
+        <v>0.9796119928359985</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009713606908917427</v>
+        <v>0.1231262907385826</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002778664929792285</v>
+        <v>0.01578642427921295</v>
       </c>
     </row>
     <row r="3">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Leucite</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.9951438307762146</v>
+        <v>0.9822190999984741</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01676768064498901</v>
+        <v>0.1119849905371666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002024916931986809</v>
+        <v>0.01035896502435207</v>
       </c>
     </row>
     <row r="4">
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.9798195362091064</v>
+        <v>0.9810236096382141</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1350377947092056</v>
+        <v>0.1144321784377098</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01945960521697998</v>
+        <v>0.01088796369731426</v>
       </c>
     </row>
     <row r="5">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Nepheline</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.994264543056488</v>
+        <v>0.9847466945648193</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02196587435901165</v>
+        <v>0.09102648496627808</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00263807806186378</v>
+        <v>0.01329232100397348</v>
       </c>
     </row>
     <row r="6">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Melilite</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.9873798489570618</v>
+        <v>0.9912225604057312</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07769082486629486</v>
+        <v>0.04795359447598457</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01226158160716295</v>
+        <v>0.004293879959732294</v>
       </c>
     </row>
   </sheetData>
